--- a/outputs/Tabla3_Prob_Excedencia_LBSPR.xlsx
+++ b/outputs/Tabla3_Prob_Excedencia_LBSPR.xlsx
@@ -20,16 +20,16 @@
     <t xml:space="preserve">FM</t>
   </si>
   <si>
-    <t xml:space="preserve">SPR_det_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_SPR40_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPR_det_MLS25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_SPR40_MLS25</t>
+    <t xml:space="preserve">SPR_det_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_SPR40_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_det_MCRS25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_SPR40_MCRS25</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA_SPR_pp</t>
